--- a/胎壓檢測器資料庫_V10/RENAULT_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/RENAULT_Data.xlsx
@@ -10155,10 +10155,26 @@
           <t>171, ACS</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>10/2007 -</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>HSS 3041</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>SCHRADER</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10243,10 +10259,26 @@
           <t>166, AJP</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>10/2007 -</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>HSS 3041</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>SCHRADER</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
